--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,10 +111,13 @@
     <t/>
   </si>
   <si>
+    <t>SubmissionSet.entryUUID</t>
+  </si>
+  <si>
+    <t>equivalent</t>
+  </si>
+  <si>
     <t>SubmissionSet.availabilityStatus</t>
-  </si>
-  <si>
-    <t>equivalent</t>
   </si>
   <si>
     <t>List.status</t>
@@ -425,7 +428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -470,88 +473,99 @@
       <c r="C3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>34</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D9" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,13 @@
     <t>Relationship</t>
   </si>
   <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/SubmissionSet|0.1.0</t>
+  </si>
+  <si>
     <t/>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm/StructureDefinition/pdsm-submissionset-comprehensive|3.1.0</t>
   </si>
   <si>
     <t>SubmissionSet.entryUUID</t>
@@ -450,120 +456,120 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2"/>
     </row>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/submissionSetToPDSM.xlsx
+++ b/add-info-dmp/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
